--- a/calibration/phase3_tp_decay/outputs/calibration_summary.xlsx
+++ b/calibration/phase3_tp_decay/outputs/calibration_summary.xlsx
@@ -498,46 +498,46 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.4976069886495024</v>
+        <v>0.5</v>
       </c>
       <c r="C2">
-        <v>0.2285370594189746</v>
+        <v>0.2166666666666667</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>31.07740552915036</v>
+        <v>33.25888936286852</v>
       </c>
       <c r="F2">
         <v>0.03</v>
       </c>
       <c r="G2">
-        <v>0.9547139563290189</v>
+        <v>0.9447248149745642</v>
       </c>
       <c r="H2">
-        <v>0.1537385232024071</v>
+        <v>0.1569172566288274</v>
       </c>
       <c r="I2">
-        <v>0.1180250284388673</v>
+        <v>0.1203784258153739</v>
       </c>
       <c r="J2">
-        <v>0.02899159408204306</v>
+        <v>0.03142403749098013</v>
       </c>
       <c r="K2">
-        <v>0.5123358214804823</v>
+        <v>0.5292363645851248</v>
       </c>
       <c r="L2">
-        <v>0.3981206042594089</v>
+        <v>0.4186202488831245</v>
       </c>
       <c r="M2">
-        <v>0.3364397709076411</v>
+        <v>0.3581749008919358</v>
       </c>
       <c r="N2">
-        <v>-144.2115858230928</v>
+        <v>-106.9364889437321</v>
       </c>
       <c r="O2">
-        <v>-128.5325936378415</v>
+        <v>-92.41011505153998</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -545,46 +545,46 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>0.3965577160403107</v>
+        <v>0.3499903676996591</v>
       </c>
       <c r="C3">
-        <v>0.02889640195313765</v>
+        <v>0.09999745027343919</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>48.36997743343321</v>
+        <v>46.04312364274379</v>
       </c>
       <c r="F3">
         <v>0.01</v>
       </c>
       <c r="G3">
-        <v>0.9366744100388968</v>
+        <v>0.9233267611798752</v>
       </c>
       <c r="H3">
-        <v>0.1362580964967874</v>
+        <v>0.158845969976101</v>
       </c>
       <c r="I3">
-        <v>0.1081870588708896</v>
+        <v>0.1262254293721227</v>
       </c>
       <c r="J3">
-        <v>0.02869691113008027</v>
+        <v>0.03322947426383489</v>
       </c>
       <c r="K3">
-        <v>0.6095139437419349</v>
+        <v>0.5770095263734242</v>
       </c>
       <c r="L3">
-        <v>0.4881729583119506</v>
+        <v>0.448984356539683</v>
       </c>
       <c r="M3">
-        <v>0.4211882632061476</v>
+        <v>0.3797468338282133</v>
       </c>
       <c r="N3">
-        <v>-39.3868665546204</v>
+        <v>-51.44873628547694</v>
       </c>
       <c r="O3">
-        <v>-30.58086597615258</v>
+        <v>-39.99643907973498</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -592,7 +592,7 @@
         <v>19</v>
       </c>
       <c r="Q4">
-        <v>0.2899966196991945</v>
+        <v>0.3157632266049284</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -600,7 +600,7 @@
         <v>20</v>
       </c>
       <c r="Q5">
-        <v>0.1010492726091917</v>
+        <v>0.1500096323003409</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -608,7 +608,7 @@
         <v>21</v>
       </c>
       <c r="Q6">
-        <v>0.1996406574658369</v>
+        <v>0.1166692163932275</v>
       </c>
     </row>
   </sheetData>
